--- a/diseases/d052/2010-2014.xlsx
+++ b/diseases/d052/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2445,9 +2439,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3285,9 +3276,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3977,9 +3965,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4817,9 +4802,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5657,9 +5639,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6349,9 +6328,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7189,9 +7165,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7881,9 +7854,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8721,9 +8691,6 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.01864506151518533</v>
       </c>
@@ -9561,9 +9528,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10253,9 +10217,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -10797,9 +10758,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11093,9 +11051,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -11637,9 +11592,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -11933,9 +11885,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12477,9 +12426,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -12773,9 +12719,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13317,9 +13260,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -13613,9 +13553,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -14157,9 +14094,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14453,9 +14387,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -14997,9 +14928,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15293,9 +15221,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -15837,9 +15762,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -16133,9 +16055,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -16677,9 +16596,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -17121,9 +17037,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -17665,9 +17578,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -17961,9 +17871,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -18505,9 +18412,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -18801,9 +18705,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19345,9 +19246,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -19641,9 +19539,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -20185,9 +20080,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -20481,9 +20373,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21025,9 +20914,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -21321,9 +21207,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -21865,9 +21748,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -22161,9 +22041,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -22705,9 +22582,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -23001,9 +22875,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -23545,9 +23416,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -23841,9 +23709,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -24385,9 +24250,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -24681,9 +24543,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -25225,9 +25084,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -25521,9 +25377,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -26065,9 +25918,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -26509,9 +26359,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -27053,9 +26900,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -27497,9 +27341,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -28041,9 +27882,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -28929,9 +28767,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -29473,9 +29308,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -30509,9 +30341,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -31053,9 +30882,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -32089,9 +31915,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -32633,9 +32456,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -33669,9 +33489,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -34213,9 +34030,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -35249,9 +35063,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -35941,9 +35752,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -36829,9 +36637,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -37521,9 +37326,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -38557,9 +38359,6 @@
       <c r="O231" t="n">
         <v>1</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -39101,9 +38900,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -40137,9 +39933,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -40681,9 +40474,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
@@ -41717,9 +41507,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -42261,9 +42048,6 @@
       <c r="O254" t="n">
         <v>0</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0</v>
       </c>
@@ -43297,9 +43081,6 @@
       <c r="O261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0</v>
       </c>
@@ -43841,9 +43622,6 @@
       <c r="O264" t="n">
         <v>1</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -44877,9 +44655,6 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -45421,9 +45196,6 @@
       <c r="O274" t="n">
         <v>1</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -46605,9 +46377,6 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0</v>
       </c>
@@ -47149,9 +46918,6 @@
       <c r="O285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -48185,9 +47951,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -48729,9 +48492,6 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -49765,9 +49525,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -50457,9 +50214,6 @@
       <c r="O306" t="n">
         <v>0</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0</v>
       </c>
@@ -51345,9 +51099,6 @@
       <c r="O312" t="n">
         <v>0</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0</v>
       </c>
@@ -51889,9 +51640,6 @@
       <c r="O315" t="n">
         <v>0</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0</v>
       </c>
@@ -53073,9 +52821,6 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
@@ -53617,9 +53362,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -54801,9 +54543,6 @@
       <c r="O334" t="n">
         <v>0</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0</v>
       </c>
@@ -55345,9 +55084,6 @@
       <c r="O337" t="n">
         <v>0</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0</v>
       </c>
@@ -56233,9 +55969,6 @@
       <c r="O343" t="n">
         <v>1</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -56777,9 +56510,6 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
@@ -57813,9 +57543,6 @@
       <c r="O353" t="n">
         <v>0</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0</v>
       </c>
@@ -58357,9 +58084,6 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0</v>
       </c>
@@ -59393,9 +59117,6 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
@@ -59937,9 +59658,6 @@
       <c r="O366" t="n">
         <v>0</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0</v>
       </c>
@@ -60973,9 +60691,6 @@
       <c r="O373" t="n">
         <v>0</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0</v>
       </c>
@@ -61517,9 +61232,6 @@
       <c r="O376" t="n">
         <v>0</v>
       </c>
-      <c r="Q376" t="n">
-        <v>0</v>
-      </c>
       <c r="R376" t="n">
         <v>0</v>
       </c>
@@ -62553,9 +62265,6 @@
       <c r="O383" t="n">
         <v>0</v>
       </c>
-      <c r="Q383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0</v>
       </c>
@@ -63097,9 +62806,6 @@
       <c r="O386" t="n">
         <v>0</v>
       </c>
-      <c r="Q386" t="n">
-        <v>0</v>
-      </c>
       <c r="R386" t="n">
         <v>0</v>
       </c>
@@ -63985,9 +63691,6 @@
       <c r="O392" t="n">
         <v>0</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0</v>
       </c>
@@ -64677,9 +64380,6 @@
       <c r="O396" t="n">
         <v>0</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>0</v>
       </c>
@@ -65713,9 +65413,6 @@
       <c r="O403" t="n">
         <v>1</v>
       </c>
-      <c r="Q403" t="n">
-        <v>0</v>
-      </c>
       <c r="R403" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -66257,9 +65954,6 @@
       <c r="O406" t="n">
         <v>0</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0</v>
       </c>
@@ -67145,9 +66839,6 @@
       <c r="O412" t="n">
         <v>0</v>
       </c>
-      <c r="Q412" t="n">
-        <v>0</v>
-      </c>
       <c r="R412" t="n">
         <v>0</v>
       </c>
@@ -67689,9 +67380,6 @@
       <c r="O415" t="n">
         <v>1</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -68725,9 +68413,6 @@
       <c r="O422" t="n">
         <v>0</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>0</v>
       </c>
@@ -69269,9 +68954,6 @@
       <c r="O425" t="n">
         <v>0</v>
       </c>
-      <c r="Q425" t="n">
-        <v>0</v>
-      </c>
       <c r="R425" t="n">
         <v>0</v>
       </c>
@@ -70305,9 +69987,6 @@
       <c r="O432" t="n">
         <v>2</v>
       </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
       <c r="R432" t="n">
         <v>0.03661874249773513</v>
       </c>
@@ -70847,9 +70526,6 @@
         <v>0</v>
       </c>
       <c r="O435" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q435" t="n">
         <v>0</v>
       </c>
       <c r="R435" t="n">
